--- a/rover_platform_mbse/export/ROVER-A1-ROVER_LOCALIZATION-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_LOCALIZATION-SWRS-V-001.xlsx
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_LOCALIZATION-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_LOCALIZATION-SWRS-V-001.xlsx
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_LOCALIZATION-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_LOCALIZATION-SWRS-V-001.xlsx
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>The rover_localization shall, when fuse_gps (default $ROVER_USE_GPS) is one of true/1/yes/on in any case and use_ekf is true, additionally start rover_ekf_global_node, rover_navsat_transform_node and rover_gps_heading_node and load the _with_gps configuration.</t>
+          <t>The rover_localization shall, when fuse_gps (default $ROVER_SYSTEM_USE_GPS) is one of true/1/yes/on in any case and use_ekf is true, additionally start rover_ekf_global_node, rover_navsat_transform_node and rover_gps_heading_node and load the _with_gps configuration.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>The rover_localization shall broadcast map -&gt; odom from rover_ekf_global_node only when publish_global_tf (default $ROVER_GPS_PUBLISH_MAP_TF) is one of true/1/yes/on, overriding the config's publish_tf.</t>
+          <t>The rover_localization shall broadcast map -&gt; odom from rover_ekf_global_node only when publish_global_tf (default $ROVER_PLATFORM_GPS_MAP_TF) is one of true/1/yes/on, overriding the config's publish_tf.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>The rover_localization launch file shall accept the arguments use_ekf (default False), fuse_gps, publish_global_tf, namespace (default $ROVER_NAMESPACE), localization_mode (rel|enu, default rel), localization_config_path, common_dir_path (default empty), use_sim (default False, sets use_sim_time) and log_level (default INFO).</t>
+          <t>The rover_localization launch file shall accept the arguments use_ekf (default False), fuse_gps, publish_global_tf, namespace (default $ROVER_SYSTEM_NAMESPACE), localization_mode (rel|enu, default rel), localization_config_path, common_dir_path (default empty), use_sim (default False, sets use_sim_time) and log_level (default INFO).</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>rover_localization is a configuration-and-launch package (no own source code) that runs robot_localization filters for the rover. In the default mode it starts rover_ekf_node, which fuses wheel-odometry body velocities and IMU yaw rate into the continuous odom -&gt; base_footprint estimate. With GPS fusion enabled (ROVER_USE_GPS) it also starts rover_ekf_global_node (map-frame filter adding GPS X/Y), rover_navsat_transform_node and rover_gps_heading_node (package rover_gps_heading). The GPS driver itself belongs to the sensor payload (rover_sensors, outside this boundary).</t>
+          <t>rover_localization is a configuration-and-launch package (no own source code) that runs robot_localization filters for the rover. In the default mode it starts rover_ekf_node, which fuses wheel-odometry body velocities and IMU yaw rate into the continuous odom -&gt; base_footprint estimate. With GPS fusion enabled (ROVER_SYSTEM_USE_GPS) it also starts rover_ekf_global_node (map-frame filter adding GPS X/Y), rover_navsat_transform_node and rover_gps_heading_node (package rover_gps_heading). The GPS driver itself belongs to the sensor payload (rover_sensors, outside this boundary).</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_LOCALIZATION-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_LOCALIZATION-SWRS-V-001.xlsx
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>The rover_localization shall broadcast map -&gt; odom from rover_ekf_global_node only when publish_global_tf (default $ROVER_PLATFORM_GPS_MAP_TF) is one of true/1/yes/on, overriding the config's publish_tf.</t>
+          <t>The rover_localization shall broadcast map -&gt; odom from rover_ekf_global_node only when publish_global_tf (default $ROVER_SYSTEM_GPS_MAP_TF) is one of true/1/yes/on, overriding the config's publish_tf.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
